--- a/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/significant_pathways_summary.xlsx
+++ b/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/significant_pathways_summary.xlsx
@@ -416,16 +416,16 @@
         </is>
       </c>
       <c r="C2">
-        <v>-1.94457242248312</v>
+        <v>-1.88825721485498</v>
       </c>
       <c r="D2">
-        <v>0.000000000000000000429576461893921</v>
+        <v>0.0000000000000000464843374321408</v>
       </c>
       <c r="E2">
-        <v>0.00000000000000000300703523325744</v>
+        <v>0.000000000000000325390362024985</v>
       </c>
       <c r="F2">
-        <v>839</v>
+        <v>858</v>
       </c>
     </row>
     <row r="3">
@@ -440,16 +440,16 @@
         </is>
       </c>
       <c r="C3">
-        <v>1.4811253577119</v>
+        <v>1.52330282167278</v>
       </c>
       <c r="D3">
-        <v>0.0000020944066603438</v>
+        <v>0.000000107966438332202</v>
       </c>
       <c r="E3">
-        <v>0.00000733042331120331</v>
+        <v>0.000000377882534162706</v>
       </c>
       <c r="F3">
-        <v>842</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4">
@@ -464,13 +464,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>-1.64966668487974</v>
+        <v>-1.66850479798948</v>
       </c>
       <c r="D4">
-        <v>0.00385786483127174</v>
+        <v>0.0039519590954491</v>
       </c>
       <c r="E4">
-        <v>0.00900168460630073</v>
+        <v>0.00922123788938124</v>
       </c>
       <c r="F4">
         <v>55</v>
